--- a/backend/src/data/consultations.xlsx
+++ b/backend/src/data/consultations.xlsx
@@ -11,42 +11,1185 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="393">
+  <si>
+    <t>Consultation ID</t>
+  </si>
+  <si>
+    <t>Patient ID</t>
+  </si>
+  <si>
+    <t>Patient Name</t>
+  </si>
   <si>
     <t>OP Number</t>
   </si>
   <si>
-    <t>Patient Name</t>
-  </si>
-  <si>
     <t>Doctor</t>
   </si>
   <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Vitals</t>
+  </si>
+  <si>
+    <t>Complaints</t>
+  </si>
+  <si>
     <t>Diagnosis</t>
   </si>
   <si>
-    <t>Prescription</t>
-  </si>
-  <si>
-    <t>Consultation Date</t>
-  </si>
-  <si>
-    <t>OP-2026-1001</t>
-  </si>
-  <si>
-    <t>Keerthika</t>
-  </si>
-  <si>
-    <t>Dr Kumar</t>
-  </si>
-  <si>
-    <t>Knee Pain</t>
-  </si>
-  <si>
-    <t>Paracetamol</t>
-  </si>
-  <si>
-    <t>31/5/2026, 3:44:41 pm</t>
+    <t>Investigations</t>
+  </si>
+  <si>
+    <t>Medicines</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>CONS-BAAE3C</t>
+  </si>
+  <si>
+    <t>PAT-A0B06C8B</t>
+  </si>
+  <si>
+    <t>Rahul Nair</t>
+  </si>
+  <si>
+    <t>OP001000</t>
+  </si>
+  <si>
+    <t>Dr. Patel</t>
+  </si>
+  <si>
+    <t>General Medicine</t>
+  </si>
+  <si>
+    <t>Waiting</t>
+  </si>
+  <si>
+    <t>2026-06-04T05:28:42.592Z</t>
+  </si>
+  <si>
+    <t>{"bp":"120/80","pulse":"75","weight":"70","temp":"98.6"}</t>
+  </si>
+  <si>
+    <t>Knee pain</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>Advised rest and hot fomentation</t>
+  </si>
+  <si>
+    <t>CONS-2631B0</t>
+  </si>
+  <si>
+    <t>PAT-8F6D5E18</t>
+  </si>
+  <si>
+    <t>Arjun Chowdary</t>
+  </si>
+  <si>
+    <t>OP001001</t>
+  </si>
+  <si>
+    <t>Dr. Reddy</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Chronic knee pain for 2 weeks</t>
+  </si>
+  <si>
+    <t>Mild Osteoarthritis</t>
+  </si>
+  <si>
+    <t>["X-Ray Knee AP/Lat"]</t>
+  </si>
+  <si>
+    <t>[{"name":"Paracetamol 500mg","dosage":"1-0-1","days":5}]</t>
+  </si>
+  <si>
+    <t>CONS-DE99CF</t>
+  </si>
+  <si>
+    <t>PAT-A86C5C37</t>
+  </si>
+  <si>
+    <t>Ananya Menon</t>
+  </si>
+  <si>
+    <t>OP001002</t>
+  </si>
+  <si>
+    <t>Physiotherapy</t>
+  </si>
+  <si>
+    <t>CONS-27D6CA</t>
+  </si>
+  <si>
+    <t>PAT-A93ED4E0</t>
+  </si>
+  <si>
+    <t>Sunita Rao</t>
+  </si>
+  <si>
+    <t>OP001003</t>
+  </si>
+  <si>
+    <t>Dr. Sharma</t>
+  </si>
+  <si>
+    <t>CONS-4297F1</t>
+  </si>
+  <si>
+    <t>PAT-13B27116</t>
+  </si>
+  <si>
+    <t>Vihaan Reddy</t>
+  </si>
+  <si>
+    <t>OP001004</t>
+  </si>
+  <si>
+    <t>Orthopaedics</t>
+  </si>
+  <si>
+    <t>CONS-4A06E9</t>
+  </si>
+  <si>
+    <t>PAT-484C48C4</t>
+  </si>
+  <si>
+    <t>Ishita Reddy</t>
+  </si>
+  <si>
+    <t>OP001005</t>
+  </si>
+  <si>
+    <t>CONS-0090F8</t>
+  </si>
+  <si>
+    <t>PAT-13C4476C</t>
+  </si>
+  <si>
+    <t>OP001006</t>
+  </si>
+  <si>
+    <t>CONS-026036</t>
+  </si>
+  <si>
+    <t>PAT-DE82E56C</t>
+  </si>
+  <si>
+    <t>Krishna Sharma</t>
+  </si>
+  <si>
+    <t>OP001007</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>CONS-9B78E0</t>
+  </si>
+  <si>
+    <t>PAT-5ECBAE08</t>
+  </si>
+  <si>
+    <t>Krishna Singh</t>
+  </si>
+  <si>
+    <t>OP001008</t>
+  </si>
+  <si>
+    <t>CONS-CE68DA</t>
+  </si>
+  <si>
+    <t>PAT-35485F8F</t>
+  </si>
+  <si>
+    <t>Neha Nair</t>
+  </si>
+  <si>
+    <t>OP001009</t>
+  </si>
+  <si>
+    <t>CONS-10BA3A</t>
+  </si>
+  <si>
+    <t>PAT-8AB3F365</t>
+  </si>
+  <si>
+    <t>Rohan Iyer</t>
+  </si>
+  <si>
+    <t>OP001010</t>
+  </si>
+  <si>
+    <t>CONS-A2D92E</t>
+  </si>
+  <si>
+    <t>PAT-DD356E59</t>
+  </si>
+  <si>
+    <t>Vikram Reddy</t>
+  </si>
+  <si>
+    <t>OP001011</t>
+  </si>
+  <si>
+    <t>CONS-3F8086</t>
+  </si>
+  <si>
+    <t>PAT-0E400A4B</t>
+  </si>
+  <si>
+    <t>Ishita Rao</t>
+  </si>
+  <si>
+    <t>OP001012</t>
+  </si>
+  <si>
+    <t>CONS-EDF8D1</t>
+  </si>
+  <si>
+    <t>PAT-EB04E49E</t>
+  </si>
+  <si>
+    <t>Vikram Singh</t>
+  </si>
+  <si>
+    <t>OP001013</t>
+  </si>
+  <si>
+    <t>CONS-83A61F</t>
+  </si>
+  <si>
+    <t>PAT-465A4CC0</t>
+  </si>
+  <si>
+    <t>Krishna Patel</t>
+  </si>
+  <si>
+    <t>OP001014</t>
+  </si>
+  <si>
+    <t>CONS-157528</t>
+  </si>
+  <si>
+    <t>PAT-1DE14465</t>
+  </si>
+  <si>
+    <t>Arjun Sharma</t>
+  </si>
+  <si>
+    <t>OP001015</t>
+  </si>
+  <si>
+    <t>CONS-4F3C90</t>
+  </si>
+  <si>
+    <t>PAT-9F3D187E</t>
+  </si>
+  <si>
+    <t>Karan Patel</t>
+  </si>
+  <si>
+    <t>OP001016</t>
+  </si>
+  <si>
+    <t>CONS-C0C587</t>
+  </si>
+  <si>
+    <t>PAT-66ED3959</t>
+  </si>
+  <si>
+    <t>Sneha Patel</t>
+  </si>
+  <si>
+    <t>OP001017</t>
+  </si>
+  <si>
+    <t>CONS-1AC711</t>
+  </si>
+  <si>
+    <t>PAT-0F4F5689</t>
+  </si>
+  <si>
+    <t>Ravi Patel</t>
+  </si>
+  <si>
+    <t>OP001018</t>
+  </si>
+  <si>
+    <t>CONS-899000</t>
+  </si>
+  <si>
+    <t>PAT-B3A40BD2</t>
+  </si>
+  <si>
+    <t>Priya Kumar</t>
+  </si>
+  <si>
+    <t>OP001019</t>
+  </si>
+  <si>
+    <t>CONS-E2191E</t>
+  </si>
+  <si>
+    <t>PAT-34B8AAC9</t>
+  </si>
+  <si>
+    <t>OP001020</t>
+  </si>
+  <si>
+    <t>CONS-0BE869</t>
+  </si>
+  <si>
+    <t>PAT-98CFBFAC</t>
+  </si>
+  <si>
+    <t>Krishna Naidu</t>
+  </si>
+  <si>
+    <t>OP001021</t>
+  </si>
+  <si>
+    <t>CONS-5FCFED</t>
+  </si>
+  <si>
+    <t>PAT-7964DCB0</t>
+  </si>
+  <si>
+    <t>Sneha Reddy</t>
+  </si>
+  <si>
+    <t>OP001022</t>
+  </si>
+  <si>
+    <t>CONS-13809F</t>
+  </si>
+  <si>
+    <t>PAT-B141758E</t>
+  </si>
+  <si>
+    <t>Arjun Kumar</t>
+  </si>
+  <si>
+    <t>OP001023</t>
+  </si>
+  <si>
+    <t>CONS-AE7954</t>
+  </si>
+  <si>
+    <t>PAT-36ED2284</t>
+  </si>
+  <si>
+    <t>Krishna Kumar</t>
+  </si>
+  <si>
+    <t>OP001024</t>
+  </si>
+  <si>
+    <t>CONS-2D3D64</t>
+  </si>
+  <si>
+    <t>PAT-B7D5099A</t>
+  </si>
+  <si>
+    <t>Gita Gowda</t>
+  </si>
+  <si>
+    <t>OP001025</t>
+  </si>
+  <si>
+    <t>CONS-C9E5E9</t>
+  </si>
+  <si>
+    <t>PAT-BFA29F5D</t>
+  </si>
+  <si>
+    <t>Ravi Gowda</t>
+  </si>
+  <si>
+    <t>OP001026</t>
+  </si>
+  <si>
+    <t>CONS-3CB12D</t>
+  </si>
+  <si>
+    <t>PAT-25B64058</t>
+  </si>
+  <si>
+    <t>Neha Gowda</t>
+  </si>
+  <si>
+    <t>OP001027</t>
+  </si>
+  <si>
+    <t>CONS-0FC34B</t>
+  </si>
+  <si>
+    <t>PAT-17594EA1</t>
+  </si>
+  <si>
+    <t>Vihaan Patel</t>
+  </si>
+  <si>
+    <t>OP001028</t>
+  </si>
+  <si>
+    <t>CONS-984241</t>
+  </si>
+  <si>
+    <t>PAT-4D979A6B</t>
+  </si>
+  <si>
+    <t>Sai Kumar</t>
+  </si>
+  <si>
+    <t>OP001029</t>
+  </si>
+  <si>
+    <t>CONS-C918DA</t>
+  </si>
+  <si>
+    <t>PAT-4AAA3C1D</t>
+  </si>
+  <si>
+    <t>Sai Iyer</t>
+  </si>
+  <si>
+    <t>OP001030</t>
+  </si>
+  <si>
+    <t>2026-06-04T05:28:42.590Z</t>
+  </si>
+  <si>
+    <t>CONS-0EA0BA</t>
+  </si>
+  <si>
+    <t>PAT-781A17D8</t>
+  </si>
+  <si>
+    <t>Vikram Chowdary</t>
+  </si>
+  <si>
+    <t>OP001031</t>
+  </si>
+  <si>
+    <t>CONS-8845A9</t>
+  </si>
+  <si>
+    <t>PAT-CFF19A49</t>
+  </si>
+  <si>
+    <t>Saanvi Kumar</t>
+  </si>
+  <si>
+    <t>OP001032</t>
+  </si>
+  <si>
+    <t>CONS-057392</t>
+  </si>
+  <si>
+    <t>PAT-49C949AC</t>
+  </si>
+  <si>
+    <t>Pooja Reddy</t>
+  </si>
+  <si>
+    <t>OP001033</t>
+  </si>
+  <si>
+    <t>CONS-D3AB69</t>
+  </si>
+  <si>
+    <t>PAT-FF3DAE13</t>
+  </si>
+  <si>
+    <t>Ravi Sharma</t>
+  </si>
+  <si>
+    <t>OP001034</t>
+  </si>
+  <si>
+    <t>CONS-23E4B2</t>
+  </si>
+  <si>
+    <t>PAT-4D33A850</t>
+  </si>
+  <si>
+    <t>Rohan Singh</t>
+  </si>
+  <si>
+    <t>OP001035</t>
+  </si>
+  <si>
+    <t>2026-06-04T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-416F8C</t>
+  </si>
+  <si>
+    <t>PAT-C761C153</t>
+  </si>
+  <si>
+    <t>Aarav Gowda</t>
+  </si>
+  <si>
+    <t>OP001036</t>
+  </si>
+  <si>
+    <t>CONS-995D5D</t>
+  </si>
+  <si>
+    <t>PAT-F72FA1CE</t>
+  </si>
+  <si>
+    <t>Sneha Naidu</t>
+  </si>
+  <si>
+    <t>OP001037</t>
+  </si>
+  <si>
+    <t>CONS-354C83</t>
+  </si>
+  <si>
+    <t>PAT-76C4D01B</t>
+  </si>
+  <si>
+    <t>Gita Sharma</t>
+  </si>
+  <si>
+    <t>OP001038</t>
+  </si>
+  <si>
+    <t>CONS-5F511B</t>
+  </si>
+  <si>
+    <t>PAT-D1E00955</t>
+  </si>
+  <si>
+    <t>Saanvi Reddy</t>
+  </si>
+  <si>
+    <t>OP001039</t>
+  </si>
+  <si>
+    <t>CONS-2A7225</t>
+  </si>
+  <si>
+    <t>PAT-2184465F</t>
+  </si>
+  <si>
+    <t>Rohan Naidu</t>
+  </si>
+  <si>
+    <t>OP001040</t>
+  </si>
+  <si>
+    <t>2026-05-08T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-EDF018</t>
+  </si>
+  <si>
+    <t>PAT-DD72FDB4</t>
+  </si>
+  <si>
+    <t>Vihaan Naidu</t>
+  </si>
+  <si>
+    <t>OP001041</t>
+  </si>
+  <si>
+    <t>2026-05-20T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-A8045D</t>
+  </si>
+  <si>
+    <t>PAT-5047FBFC</t>
+  </si>
+  <si>
+    <t>Krishna Reddy</t>
+  </si>
+  <si>
+    <t>OP001042</t>
+  </si>
+  <si>
+    <t>2026-05-13T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-BB4F9B</t>
+  </si>
+  <si>
+    <t>PAT-7A11566E</t>
+  </si>
+  <si>
+    <t>Suresh Kumar</t>
+  </si>
+  <si>
+    <t>OP001043</t>
+  </si>
+  <si>
+    <t>2026-05-25T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-D35AF7</t>
+  </si>
+  <si>
+    <t>PAT-3F93F395</t>
+  </si>
+  <si>
+    <t>Ananya Kumar</t>
+  </si>
+  <si>
+    <t>OP001044</t>
+  </si>
+  <si>
+    <t>CONS-B8252C</t>
+  </si>
+  <si>
+    <t>PAT-3BDD997D</t>
+  </si>
+  <si>
+    <t>Karan Iyer</t>
+  </si>
+  <si>
+    <t>OP001045</t>
+  </si>
+  <si>
+    <t>2026-06-01T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-788329</t>
+  </si>
+  <si>
+    <t>PAT-803D4F4F</t>
+  </si>
+  <si>
+    <t>Aditya Gowda</t>
+  </si>
+  <si>
+    <t>OP001046</t>
+  </si>
+  <si>
+    <t>2026-05-21T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-E123B0</t>
+  </si>
+  <si>
+    <t>PAT-33C276EB</t>
+  </si>
+  <si>
+    <t>Suresh Reddy</t>
+  </si>
+  <si>
+    <t>OP001047</t>
+  </si>
+  <si>
+    <t>2026-06-03T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-DDE1EB</t>
+  </si>
+  <si>
+    <t>PAT-3096F817</t>
+  </si>
+  <si>
+    <t>Ishita Singh</t>
+  </si>
+  <si>
+    <t>OP001048</t>
+  </si>
+  <si>
+    <t>2026-05-17T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-C677C6</t>
+  </si>
+  <si>
+    <t>PAT-47A17A5B</t>
+  </si>
+  <si>
+    <t>OP001049</t>
+  </si>
+  <si>
+    <t>CONS-30FAAE</t>
+  </si>
+  <si>
+    <t>PAT-FBECB832</t>
+  </si>
+  <si>
+    <t>Ravi Nair</t>
+  </si>
+  <si>
+    <t>OP001050</t>
+  </si>
+  <si>
+    <t>CONS-F350B7</t>
+  </si>
+  <si>
+    <t>PAT-70C54A7D</t>
+  </si>
+  <si>
+    <t>Priya Reddy</t>
+  </si>
+  <si>
+    <t>OP001051</t>
+  </si>
+  <si>
+    <t>CONS-FD94EF</t>
+  </si>
+  <si>
+    <t>PAT-CCD0EAE1</t>
+  </si>
+  <si>
+    <t>Ramesh Iyer</t>
+  </si>
+  <si>
+    <t>OP001052</t>
+  </si>
+  <si>
+    <t>CONS-186F2B</t>
+  </si>
+  <si>
+    <t>PAT-823DC348</t>
+  </si>
+  <si>
+    <t>Arjun Iyer</t>
+  </si>
+  <si>
+    <t>OP001053</t>
+  </si>
+  <si>
+    <t>2026-05-10T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-EAC4E9</t>
+  </si>
+  <si>
+    <t>PAT-9D80B7CE</t>
+  </si>
+  <si>
+    <t>OP001054</t>
+  </si>
+  <si>
+    <t>2026-05-23T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-FEAA29</t>
+  </si>
+  <si>
+    <t>PAT-88733246</t>
+  </si>
+  <si>
+    <t>Sunita Singh</t>
+  </si>
+  <si>
+    <t>OP001055</t>
+  </si>
+  <si>
+    <t>2026-05-11T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-34724A</t>
+  </si>
+  <si>
+    <t>PAT-5DFA9F77</t>
+  </si>
+  <si>
+    <t>Krishna Iyer</t>
+  </si>
+  <si>
+    <t>OP001056</t>
+  </si>
+  <si>
+    <t>CONS-5D4373</t>
+  </si>
+  <si>
+    <t>PAT-0F1616F4</t>
+  </si>
+  <si>
+    <t>Priya Sharma</t>
+  </si>
+  <si>
+    <t>OP001057</t>
+  </si>
+  <si>
+    <t>CONS-B7D392</t>
+  </si>
+  <si>
+    <t>PAT-8262E439</t>
+  </si>
+  <si>
+    <t>Ravi Kumar</t>
+  </si>
+  <si>
+    <t>OP001058</t>
+  </si>
+  <si>
+    <t>2026-05-16T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-9C0ED1</t>
+  </si>
+  <si>
+    <t>PAT-84C6B92B</t>
+  </si>
+  <si>
+    <t>Saanvi Sharma</t>
+  </si>
+  <si>
+    <t>OP001059</t>
+  </si>
+  <si>
+    <t>CONS-CB5A74</t>
+  </si>
+  <si>
+    <t>PAT-A867E17B</t>
+  </si>
+  <si>
+    <t>Kavya Naidu</t>
+  </si>
+  <si>
+    <t>OP001060</t>
+  </si>
+  <si>
+    <t>2026-05-15T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-93027F</t>
+  </si>
+  <si>
+    <t>PAT-F9B33C3F</t>
+  </si>
+  <si>
+    <t>Suresh Nair</t>
+  </si>
+  <si>
+    <t>OP001061</t>
+  </si>
+  <si>
+    <t>2026-05-24T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-DC4302</t>
+  </si>
+  <si>
+    <t>PAT-3235C40A</t>
+  </si>
+  <si>
+    <t>Ramesh Singh</t>
+  </si>
+  <si>
+    <t>OP001062</t>
+  </si>
+  <si>
+    <t>2026-05-26T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-143224</t>
+  </si>
+  <si>
+    <t>PAT-28676C2F</t>
+  </si>
+  <si>
+    <t>Arjun Gowda</t>
+  </si>
+  <si>
+    <t>OP001063</t>
+  </si>
+  <si>
+    <t>2026-05-18T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-A9BD40</t>
+  </si>
+  <si>
+    <t>PAT-4BBE8752</t>
+  </si>
+  <si>
+    <t>Ananya Gowda</t>
+  </si>
+  <si>
+    <t>OP001064</t>
+  </si>
+  <si>
+    <t>2026-05-19T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-5D0441</t>
+  </si>
+  <si>
+    <t>PAT-0F971607</t>
+  </si>
+  <si>
+    <t>Sunita Sharma</t>
+  </si>
+  <si>
+    <t>OP001065</t>
+  </si>
+  <si>
+    <t>2026-05-14T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-EEE158</t>
+  </si>
+  <si>
+    <t>PAT-C9E559B9</t>
+  </si>
+  <si>
+    <t>Vihaan Rao</t>
+  </si>
+  <si>
+    <t>OP001066</t>
+  </si>
+  <si>
+    <t>CONS-95904D</t>
+  </si>
+  <si>
+    <t>PAT-D3266763</t>
+  </si>
+  <si>
+    <t>Gita Chowdary</t>
+  </si>
+  <si>
+    <t>OP001067</t>
+  </si>
+  <si>
+    <t>CONS-A0EEEB</t>
+  </si>
+  <si>
+    <t>PAT-22E2B37F</t>
+  </si>
+  <si>
+    <t>Suresh Naidu</t>
+  </si>
+  <si>
+    <t>OP001068</t>
+  </si>
+  <si>
+    <t>2026-05-09T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-E36314</t>
+  </si>
+  <si>
+    <t>PAT-3FE16E6C</t>
+  </si>
+  <si>
+    <t>Kavya Reddy</t>
+  </si>
+  <si>
+    <t>OP001069</t>
+  </si>
+  <si>
+    <t>CONS-4C3A47</t>
+  </si>
+  <si>
+    <t>PAT-5274D508</t>
+  </si>
+  <si>
+    <t>Saanvi Naidu</t>
+  </si>
+  <si>
+    <t>OP001070</t>
+  </si>
+  <si>
+    <t>CONS-F04339</t>
+  </si>
+  <si>
+    <t>PAT-C3AFBC88</t>
+  </si>
+  <si>
+    <t>Sai Sharma</t>
+  </si>
+  <si>
+    <t>OP001071</t>
+  </si>
+  <si>
+    <t>CONS-AD07C6</t>
+  </si>
+  <si>
+    <t>PAT-6EA9479A</t>
+  </si>
+  <si>
+    <t>OP001072</t>
+  </si>
+  <si>
+    <t>2026-05-27T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-97C921</t>
+  </si>
+  <si>
+    <t>PAT-2FA40757</t>
+  </si>
+  <si>
+    <t>Rohan Sharma</t>
+  </si>
+  <si>
+    <t>OP001073</t>
+  </si>
+  <si>
+    <t>2026-05-29T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-955123</t>
+  </si>
+  <si>
+    <t>PAT-3B550FD8</t>
+  </si>
+  <si>
+    <t>Priya Nair</t>
+  </si>
+  <si>
+    <t>OP001074</t>
+  </si>
+  <si>
+    <t>CONS-02C0DE</t>
+  </si>
+  <si>
+    <t>PAT-28DB391F</t>
+  </si>
+  <si>
+    <t>Rahul Reddy</t>
+  </si>
+  <si>
+    <t>OP001075</t>
+  </si>
+  <si>
+    <t>2026-05-06T05:28:42.591Z</t>
+  </si>
+  <si>
+    <t>CONS-1CFC3F</t>
+  </si>
+  <si>
+    <t>PAT-6B45DE9E</t>
+  </si>
+  <si>
+    <t>OP001076</t>
+  </si>
+  <si>
+    <t>CONS-AF01B6</t>
+  </si>
+  <si>
+    <t>PAT-C039E7F8</t>
+  </si>
+  <si>
+    <t>OP001077</t>
+  </si>
+  <si>
+    <t>CONS-D5D5AA</t>
+  </si>
+  <si>
+    <t>PAT-0C7DABC1</t>
+  </si>
+  <si>
+    <t>Sunita Gowda</t>
+  </si>
+  <si>
+    <t>OP001078</t>
+  </si>
+  <si>
+    <t>CONS-DC9B6F</t>
+  </si>
+  <si>
+    <t>PAT-082904B4</t>
+  </si>
+  <si>
+    <t>Vikram Sharma</t>
+  </si>
+  <si>
+    <t>OP001079</t>
+  </si>
+  <si>
+    <t>CONS-A1</t>
+  </si>
+  <si>
+    <t>PAT-8FB9A9F4</t>
+  </si>
+  <si>
+    <t>Scenario A Patient</t>
+  </si>
+  <si>
+    <t>OP002000</t>
+  </si>
+  <si>
+    <t>2026-06-04T05:28:42.593Z</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Joint pain</t>
+  </si>
+  <si>
+    <t>Sprain</t>
+  </si>
+  <si>
+    <t>CONS-B1</t>
+  </si>
+  <si>
+    <t>PAT-9F41BBA2</t>
+  </si>
+  <si>
+    <t>Scenario B Patient</t>
+  </si>
+  <si>
+    <t>OP002001</t>
+  </si>
+  <si>
+    <t>Severe back pain</t>
+  </si>
+  <si>
+    <t>Slipped Disc</t>
+  </si>
+  <si>
+    <t>["MRI Lumbar Spine"]</t>
+  </si>
+  <si>
+    <t>[{"name":"Diclofenac Gel","dosage":"Local","days":10}]</t>
+  </si>
+  <si>
+    <t>CONS-C1</t>
+  </si>
+  <si>
+    <t>PAT-006DBDB4</t>
+  </si>
+  <si>
+    <t>Scenario C Patient</t>
+  </si>
+  <si>
+    <t>OP002002</t>
+  </si>
+  <si>
+    <t>Meniscus tear</t>
+  </si>
+  <si>
+    <t>Tear</t>
+  </si>
+  <si>
+    <t>Surgery planned</t>
   </si>
 </sst>
 </file>
@@ -423,16 +1566,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="3" width="25" customWidth="1"/>
-    <col min="4" max="5" width="40" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="13" width="40" customWidth="1"/>
+    <col min="14" max="14" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -451,25 +1601,3681 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L11" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" t="s">
+        <v>34</v>
+      </c>
+      <c r="L13" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
+        <v>33</v>
+      </c>
+      <c r="K16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s">
+        <v>25</v>
+      </c>
+      <c r="N16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" t="s">
+        <v>35</v>
+      </c>
+      <c r="M18" t="s">
+        <v>36</v>
+      </c>
+      <c r="N18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" t="s">
+        <v>33</v>
+      </c>
+      <c r="K19" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" t="s">
+        <v>35</v>
+      </c>
+      <c r="M19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M20" t="s">
+        <v>36</v>
+      </c>
+      <c r="N20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M21" t="s">
+        <v>36</v>
+      </c>
+      <c r="N21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" t="s">
+        <v>33</v>
+      </c>
+      <c r="K23" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" t="s">
+        <v>25</v>
+      </c>
+      <c r="N23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" t="s">
+        <v>35</v>
+      </c>
+      <c r="M24" t="s">
+        <v>36</v>
+      </c>
+      <c r="N24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" t="s">
+        <v>33</v>
+      </c>
+      <c r="K25" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" t="s">
+        <v>35</v>
+      </c>
+      <c r="M25" t="s">
+        <v>36</v>
+      </c>
+      <c r="N25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" t="s">
+        <v>33</v>
+      </c>
+      <c r="K26" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" t="s">
+        <v>35</v>
+      </c>
+      <c r="M26" t="s">
+        <v>36</v>
+      </c>
+      <c r="N26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" t="s">
+        <v>33</v>
+      </c>
+      <c r="K27" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" t="s">
+        <v>35</v>
+      </c>
+      <c r="M27" t="s">
+        <v>36</v>
+      </c>
+      <c r="N27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" t="s">
+        <v>35</v>
+      </c>
+      <c r="M28" t="s">
+        <v>36</v>
+      </c>
+      <c r="N28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" t="s">
+        <v>33</v>
+      </c>
+      <c r="K29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" t="s">
+        <v>35</v>
+      </c>
+      <c r="M29" t="s">
+        <v>36</v>
+      </c>
+      <c r="N29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" t="s">
+        <v>63</v>
+      </c>
+      <c r="H30" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" t="s">
+        <v>25</v>
+      </c>
+      <c r="N30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C31" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" t="s">
+        <v>33</v>
+      </c>
+      <c r="K31" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" t="s">
+        <v>35</v>
+      </c>
+      <c r="M31" t="s">
+        <v>36</v>
+      </c>
+      <c r="N31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>151</v>
+      </c>
+      <c r="B32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" t="s">
+        <v>155</v>
+      </c>
+      <c r="I32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" t="s">
+        <v>25</v>
+      </c>
+      <c r="N32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>156</v>
+      </c>
+      <c r="B33" t="s">
+        <v>157</v>
+      </c>
+      <c r="C33" t="s">
+        <v>158</v>
+      </c>
+      <c r="D33" t="s">
+        <v>159</v>
+      </c>
+      <c r="E33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" t="s">
+        <v>155</v>
+      </c>
+      <c r="I33" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" t="s">
+        <v>33</v>
+      </c>
+      <c r="K33" t="s">
+        <v>34</v>
+      </c>
+      <c r="L33" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" t="s">
+        <v>36</v>
+      </c>
+      <c r="N33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>160</v>
+      </c>
+      <c r="B34" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" t="s">
+        <v>163</v>
+      </c>
+      <c r="E34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" t="s">
+        <v>155</v>
+      </c>
+      <c r="I34" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" t="s">
+        <v>33</v>
+      </c>
+      <c r="K34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" t="s">
+        <v>35</v>
+      </c>
+      <c r="M34" t="s">
+        <v>36</v>
+      </c>
+      <c r="N34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" t="s">
+        <v>166</v>
+      </c>
+      <c r="D35" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35" t="s">
+        <v>31</v>
+      </c>
+      <c r="F35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" t="s">
+        <v>155</v>
+      </c>
+      <c r="I35" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" t="s">
+        <v>33</v>
+      </c>
+      <c r="K35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35" t="s">
+        <v>35</v>
+      </c>
+      <c r="M35" t="s">
+        <v>36</v>
+      </c>
+      <c r="N35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" t="s">
+        <v>169</v>
+      </c>
+      <c r="C36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" t="s">
+        <v>155</v>
+      </c>
+      <c r="I36" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" t="s">
+        <v>33</v>
+      </c>
+      <c r="K36" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" t="s">
+        <v>35</v>
+      </c>
+      <c r="M36" t="s">
+        <v>36</v>
+      </c>
+      <c r="N36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>172</v>
+      </c>
+      <c r="B37" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37" t="s">
+        <v>63</v>
+      </c>
+      <c r="H37" t="s">
+        <v>176</v>
+      </c>
+      <c r="I37" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" t="s">
+        <v>33</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37" t="s">
+        <v>25</v>
+      </c>
+      <c r="N37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>177</v>
+      </c>
+      <c r="B38" t="s">
+        <v>178</v>
+      </c>
+      <c r="C38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D38" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" t="s">
+        <v>176</v>
+      </c>
+      <c r="I38" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" t="s">
+        <v>33</v>
+      </c>
+      <c r="K38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M38" t="s">
+        <v>36</v>
+      </c>
+      <c r="N38" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>181</v>
+      </c>
+      <c r="B39" t="s">
+        <v>182</v>
+      </c>
+      <c r="C39" t="s">
+        <v>183</v>
+      </c>
+      <c r="D39" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" t="s">
+        <v>51</v>
+      </c>
+      <c r="G39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" t="s">
+        <v>176</v>
+      </c>
+      <c r="I39" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" t="s">
+        <v>33</v>
+      </c>
+      <c r="K39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" t="s">
+        <v>35</v>
+      </c>
+      <c r="M39" t="s">
+        <v>36</v>
+      </c>
+      <c r="N39" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40" t="s">
+        <v>186</v>
+      </c>
+      <c r="C40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D40" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" t="s">
+        <v>46</v>
+      </c>
+      <c r="F40" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" t="s">
+        <v>176</v>
+      </c>
+      <c r="I40" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" t="s">
+        <v>33</v>
+      </c>
+      <c r="K40" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M40" t="s">
+        <v>36</v>
+      </c>
+      <c r="N40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>189</v>
+      </c>
+      <c r="B41" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" t="s">
+        <v>191</v>
+      </c>
+      <c r="D41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" t="s">
+        <v>41</v>
+      </c>
+      <c r="G41" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" t="s">
+        <v>176</v>
+      </c>
+      <c r="I41" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" t="s">
+        <v>33</v>
+      </c>
+      <c r="K41" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41" t="s">
+        <v>35</v>
+      </c>
+      <c r="M41" t="s">
+        <v>36</v>
+      </c>
+      <c r="N41" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>193</v>
+      </c>
+      <c r="B42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" t="s">
+        <v>195</v>
+      </c>
+      <c r="D42" t="s">
+        <v>196</v>
+      </c>
+      <c r="E42" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" t="s">
+        <v>51</v>
+      </c>
+      <c r="G42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" t="s">
+        <v>197</v>
+      </c>
+      <c r="I42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" t="s">
+        <v>23</v>
+      </c>
+      <c r="K42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" t="s">
+        <v>25</v>
+      </c>
+      <c r="N42" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>198</v>
+      </c>
+      <c r="B43" t="s">
+        <v>199</v>
+      </c>
+      <c r="C43" t="s">
+        <v>200</v>
+      </c>
+      <c r="D43" t="s">
+        <v>201</v>
+      </c>
+      <c r="E43" t="s">
+        <v>31</v>
+      </c>
+      <c r="F43" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" t="s">
+        <v>32</v>
+      </c>
+      <c r="H43" t="s">
+        <v>202</v>
+      </c>
+      <c r="I43" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" t="s">
+        <v>33</v>
+      </c>
+      <c r="K43" t="s">
+        <v>34</v>
+      </c>
+      <c r="L43" t="s">
+        <v>35</v>
+      </c>
+      <c r="M43" t="s">
+        <v>36</v>
+      </c>
+      <c r="N43" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>203</v>
+      </c>
+      <c r="B44" t="s">
+        <v>204</v>
+      </c>
+      <c r="C44" t="s">
+        <v>205</v>
+      </c>
+      <c r="D44" t="s">
+        <v>206</v>
+      </c>
+      <c r="E44" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" t="s">
+        <v>63</v>
+      </c>
+      <c r="H44" t="s">
+        <v>207</v>
+      </c>
+      <c r="I44" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" t="s">
+        <v>33</v>
+      </c>
+      <c r="K44" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" t="s">
+        <v>25</v>
+      </c>
+      <c r="N44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" t="s">
+        <v>209</v>
+      </c>
+      <c r="C45" t="s">
+        <v>210</v>
+      </c>
+      <c r="D45" t="s">
+        <v>211</v>
+      </c>
+      <c r="E45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" t="s">
+        <v>51</v>
+      </c>
+      <c r="G45" t="s">
+        <v>32</v>
+      </c>
+      <c r="H45" t="s">
+        <v>212</v>
+      </c>
+      <c r="I45" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" t="s">
+        <v>33</v>
+      </c>
+      <c r="K45" t="s">
+        <v>34</v>
+      </c>
+      <c r="L45" t="s">
+        <v>35</v>
+      </c>
+      <c r="M45" t="s">
+        <v>36</v>
+      </c>
+      <c r="N45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>213</v>
+      </c>
+      <c r="B46" t="s">
+        <v>214</v>
+      </c>
+      <c r="C46" t="s">
+        <v>215</v>
+      </c>
+      <c r="D46" t="s">
+        <v>216</v>
+      </c>
+      <c r="E46" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" t="s">
+        <v>41</v>
+      </c>
+      <c r="G46" t="s">
+        <v>32</v>
+      </c>
+      <c r="H46" t="s">
+        <v>202</v>
+      </c>
+      <c r="I46" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" t="s">
+        <v>33</v>
+      </c>
+      <c r="K46" t="s">
+        <v>34</v>
+      </c>
+      <c r="L46" t="s">
+        <v>35</v>
+      </c>
+      <c r="M46" t="s">
+        <v>36</v>
+      </c>
+      <c r="N46" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>217</v>
+      </c>
+      <c r="B47" t="s">
+        <v>218</v>
+      </c>
+      <c r="C47" t="s">
+        <v>219</v>
+      </c>
+      <c r="D47" t="s">
+        <v>220</v>
+      </c>
+      <c r="E47" t="s">
+        <v>31</v>
+      </c>
+      <c r="F47" t="s">
+        <v>51</v>
+      </c>
+      <c r="G47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" t="s">
+        <v>221</v>
+      </c>
+      <c r="I47" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" t="s">
+        <v>33</v>
+      </c>
+      <c r="K47" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47" t="s">
+        <v>35</v>
+      </c>
+      <c r="M47" t="s">
+        <v>36</v>
+      </c>
+      <c r="N47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>222</v>
+      </c>
+      <c r="B48" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" t="s">
+        <v>224</v>
+      </c>
+      <c r="D48" t="s">
+        <v>225</v>
+      </c>
+      <c r="E48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" t="s">
+        <v>226</v>
+      </c>
+      <c r="I48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" t="s">
+        <v>33</v>
+      </c>
+      <c r="K48" t="s">
+        <v>34</v>
+      </c>
+      <c r="L48" t="s">
+        <v>35</v>
+      </c>
+      <c r="M48" t="s">
+        <v>36</v>
+      </c>
+      <c r="N48" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>227</v>
+      </c>
+      <c r="B49" t="s">
+        <v>228</v>
+      </c>
+      <c r="C49" t="s">
+        <v>229</v>
+      </c>
+      <c r="D49" t="s">
+        <v>230</v>
+      </c>
+      <c r="E49" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" t="s">
+        <v>41</v>
+      </c>
+      <c r="G49" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" t="s">
+        <v>231</v>
+      </c>
+      <c r="I49" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" t="s">
+        <v>33</v>
+      </c>
+      <c r="K49" t="s">
+        <v>34</v>
+      </c>
+      <c r="L49" t="s">
+        <v>35</v>
+      </c>
+      <c r="M49" t="s">
+        <v>36</v>
+      </c>
+      <c r="N49" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>232</v>
+      </c>
+      <c r="B50" t="s">
+        <v>233</v>
+      </c>
+      <c r="C50" t="s">
+        <v>234</v>
+      </c>
+      <c r="D50" t="s">
+        <v>235</v>
+      </c>
+      <c r="E50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" t="s">
+        <v>236</v>
+      </c>
+      <c r="I50" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" t="s">
+        <v>33</v>
+      </c>
+      <c r="K50" t="s">
+        <v>34</v>
+      </c>
+      <c r="L50" t="s">
+        <v>35</v>
+      </c>
+      <c r="M50" t="s">
+        <v>36</v>
+      </c>
+      <c r="N50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>237</v>
+      </c>
+      <c r="B51" t="s">
+        <v>238</v>
+      </c>
+      <c r="C51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D51" t="s">
+        <v>239</v>
+      </c>
+      <c r="E51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51" t="s">
+        <v>41</v>
+      </c>
+      <c r="G51" t="s">
+        <v>63</v>
+      </c>
+      <c r="H51" t="s">
+        <v>207</v>
+      </c>
+      <c r="I51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" t="s">
+        <v>33</v>
+      </c>
+      <c r="K51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" t="s">
+        <v>25</v>
+      </c>
+      <c r="M51" t="s">
+        <v>25</v>
+      </c>
+      <c r="N51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>240</v>
+      </c>
+      <c r="B52" t="s">
+        <v>241</v>
+      </c>
+      <c r="C52" t="s">
+        <v>242</v>
+      </c>
+      <c r="D52" t="s">
+        <v>243</v>
+      </c>
+      <c r="E52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F52" t="s">
+        <v>51</v>
+      </c>
+      <c r="G52" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" t="s">
+        <v>221</v>
+      </c>
+      <c r="I52" t="s">
+        <v>22</v>
+      </c>
+      <c r="J52" t="s">
+        <v>23</v>
+      </c>
+      <c r="K52" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" t="s">
+        <v>25</v>
+      </c>
+      <c r="N52" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>244</v>
+      </c>
+      <c r="B53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C53" t="s">
+        <v>246</v>
+      </c>
+      <c r="D53" t="s">
+        <v>247</v>
+      </c>
+      <c r="E53" t="s">
+        <v>31</v>
+      </c>
+      <c r="F53" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" t="s">
+        <v>32</v>
+      </c>
+      <c r="H53" t="s">
+        <v>236</v>
+      </c>
+      <c r="I53" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" t="s">
+        <v>33</v>
+      </c>
+      <c r="K53" t="s">
+        <v>34</v>
+      </c>
+      <c r="L53" t="s">
+        <v>35</v>
+      </c>
+      <c r="M53" t="s">
+        <v>36</v>
+      </c>
+      <c r="N53" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>248</v>
+      </c>
+      <c r="B54" t="s">
+        <v>249</v>
+      </c>
+      <c r="C54" t="s">
+        <v>250</v>
+      </c>
+      <c r="D54" t="s">
+        <v>251</v>
+      </c>
+      <c r="E54" t="s">
+        <v>46</v>
+      </c>
+      <c r="F54" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" t="s">
+        <v>32</v>
+      </c>
+      <c r="H54" t="s">
+        <v>236</v>
+      </c>
+      <c r="I54" t="s">
+        <v>22</v>
+      </c>
+      <c r="J54" t="s">
+        <v>33</v>
+      </c>
+      <c r="K54" t="s">
+        <v>34</v>
+      </c>
+      <c r="L54" t="s">
+        <v>35</v>
+      </c>
+      <c r="M54" t="s">
+        <v>36</v>
+      </c>
+      <c r="N54" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>252</v>
+      </c>
+      <c r="B55" t="s">
+        <v>253</v>
+      </c>
+      <c r="C55" t="s">
+        <v>254</v>
+      </c>
+      <c r="D55" t="s">
+        <v>255</v>
+      </c>
+      <c r="E55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" t="s">
+        <v>32</v>
+      </c>
+      <c r="H55" t="s">
+        <v>256</v>
+      </c>
+      <c r="I55" t="s">
+        <v>22</v>
+      </c>
+      <c r="J55" t="s">
+        <v>33</v>
+      </c>
+      <c r="K55" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55" t="s">
+        <v>35</v>
+      </c>
+      <c r="M55" t="s">
+        <v>36</v>
+      </c>
+      <c r="N55" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>257</v>
+      </c>
+      <c r="B56" t="s">
+        <v>258</v>
+      </c>
+      <c r="C56" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" t="s">
+        <v>259</v>
+      </c>
+      <c r="E56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" t="s">
+        <v>32</v>
+      </c>
+      <c r="H56" t="s">
+        <v>260</v>
+      </c>
+      <c r="I56" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" t="s">
+        <v>33</v>
+      </c>
+      <c r="K56" t="s">
+        <v>34</v>
+      </c>
+      <c r="L56" t="s">
+        <v>35</v>
+      </c>
+      <c r="M56" t="s">
+        <v>36</v>
+      </c>
+      <c r="N56" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>261</v>
+      </c>
+      <c r="B57" t="s">
+        <v>262</v>
+      </c>
+      <c r="C57" t="s">
+        <v>263</v>
+      </c>
+      <c r="D57" t="s">
+        <v>264</v>
+      </c>
+      <c r="E57" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57" t="s">
+        <v>41</v>
+      </c>
+      <c r="G57" t="s">
+        <v>32</v>
+      </c>
+      <c r="H57" t="s">
+        <v>265</v>
+      </c>
+      <c r="I57" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" t="s">
+        <v>33</v>
+      </c>
+      <c r="K57" t="s">
+        <v>34</v>
+      </c>
+      <c r="L57" t="s">
+        <v>35</v>
+      </c>
+      <c r="M57" t="s">
+        <v>36</v>
+      </c>
+      <c r="N57" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>266</v>
+      </c>
+      <c r="B58" t="s">
+        <v>267</v>
+      </c>
+      <c r="C58" t="s">
+        <v>268</v>
+      </c>
+      <c r="D58" t="s">
+        <v>269</v>
+      </c>
+      <c r="E58" t="s">
+        <v>46</v>
+      </c>
+      <c r="F58" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" t="s">
+        <v>63</v>
+      </c>
+      <c r="H58" t="s">
+        <v>226</v>
+      </c>
+      <c r="I58" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" t="s">
+        <v>33</v>
+      </c>
+      <c r="K58" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" t="s">
+        <v>25</v>
+      </c>
+      <c r="M58" t="s">
+        <v>25</v>
+      </c>
+      <c r="N58" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>270</v>
+      </c>
+      <c r="B59" t="s">
+        <v>271</v>
+      </c>
+      <c r="C59" t="s">
+        <v>272</v>
+      </c>
+      <c r="D59" t="s">
+        <v>273</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" t="s">
+        <v>51</v>
+      </c>
+      <c r="G59" t="s">
+        <v>32</v>
+      </c>
+      <c r="H59" t="s">
+        <v>265</v>
+      </c>
+      <c r="I59" t="s">
+        <v>22</v>
+      </c>
+      <c r="J59" t="s">
+        <v>33</v>
+      </c>
+      <c r="K59" t="s">
+        <v>34</v>
+      </c>
+      <c r="L59" t="s">
+        <v>35</v>
+      </c>
+      <c r="M59" t="s">
+        <v>36</v>
+      </c>
+      <c r="N59" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>274</v>
+      </c>
+      <c r="B60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" t="s">
+        <v>276</v>
+      </c>
+      <c r="D60" t="s">
+        <v>277</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>19</v>
+      </c>
+      <c r="G60" t="s">
+        <v>32</v>
+      </c>
+      <c r="H60" t="s">
+        <v>278</v>
+      </c>
+      <c r="I60" t="s">
+        <v>22</v>
+      </c>
+      <c r="J60" t="s">
+        <v>33</v>
+      </c>
+      <c r="K60" t="s">
+        <v>34</v>
+      </c>
+      <c r="L60" t="s">
+        <v>35</v>
+      </c>
+      <c r="M60" t="s">
+        <v>36</v>
+      </c>
+      <c r="N60" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>279</v>
+      </c>
+      <c r="B61" t="s">
+        <v>280</v>
+      </c>
+      <c r="C61" t="s">
+        <v>281</v>
+      </c>
+      <c r="D61" t="s">
+        <v>282</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" t="s">
+        <v>32</v>
+      </c>
+      <c r="H61" t="s">
+        <v>221</v>
+      </c>
+      <c r="I61" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" t="s">
+        <v>33</v>
+      </c>
+      <c r="K61" t="s">
+        <v>34</v>
+      </c>
+      <c r="L61" t="s">
+        <v>35</v>
+      </c>
+      <c r="M61" t="s">
+        <v>36</v>
+      </c>
+      <c r="N61" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>283</v>
+      </c>
+      <c r="B62" t="s">
+        <v>284</v>
+      </c>
+      <c r="C62" t="s">
+        <v>285</v>
+      </c>
+      <c r="D62" t="s">
+        <v>286</v>
+      </c>
+      <c r="E62" t="s">
+        <v>31</v>
+      </c>
+      <c r="F62" t="s">
+        <v>41</v>
+      </c>
+      <c r="G62" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" t="s">
+        <v>287</v>
+      </c>
+      <c r="I62" t="s">
+        <v>22</v>
+      </c>
+      <c r="J62" t="s">
+        <v>23</v>
+      </c>
+      <c r="K62" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" t="s">
+        <v>25</v>
+      </c>
+      <c r="M62" t="s">
+        <v>25</v>
+      </c>
+      <c r="N62" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>288</v>
+      </c>
+      <c r="B63" t="s">
+        <v>289</v>
+      </c>
+      <c r="C63" t="s">
+        <v>290</v>
+      </c>
+      <c r="D63" t="s">
+        <v>291</v>
+      </c>
+      <c r="E63" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G63" t="s">
+        <v>32</v>
+      </c>
+      <c r="H63" t="s">
+        <v>292</v>
+      </c>
+      <c r="I63" t="s">
+        <v>22</v>
+      </c>
+      <c r="J63" t="s">
+        <v>33</v>
+      </c>
+      <c r="K63" t="s">
+        <v>34</v>
+      </c>
+      <c r="L63" t="s">
+        <v>35</v>
+      </c>
+      <c r="M63" t="s">
+        <v>36</v>
+      </c>
+      <c r="N63" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>293</v>
+      </c>
+      <c r="B64" t="s">
+        <v>294</v>
+      </c>
+      <c r="C64" t="s">
+        <v>295</v>
+      </c>
+      <c r="D64" t="s">
+        <v>296</v>
+      </c>
+      <c r="E64" t="s">
+        <v>46</v>
+      </c>
+      <c r="F64" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" t="s">
+        <v>32</v>
+      </c>
+      <c r="H64" t="s">
+        <v>297</v>
+      </c>
+      <c r="I64" t="s">
+        <v>22</v>
+      </c>
+      <c r="J64" t="s">
+        <v>33</v>
+      </c>
+      <c r="K64" t="s">
+        <v>34</v>
+      </c>
+      <c r="L64" t="s">
+        <v>35</v>
+      </c>
+      <c r="M64" t="s">
+        <v>36</v>
+      </c>
+      <c r="N64" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>298</v>
+      </c>
+      <c r="B65" t="s">
+        <v>299</v>
+      </c>
+      <c r="C65" t="s">
+        <v>300</v>
+      </c>
+      <c r="D65" t="s">
+        <v>301</v>
+      </c>
+      <c r="E65" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" t="s">
+        <v>63</v>
+      </c>
+      <c r="H65" t="s">
+        <v>302</v>
+      </c>
+      <c r="I65" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" t="s">
+        <v>33</v>
+      </c>
+      <c r="K65" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" t="s">
+        <v>25</v>
+      </c>
+      <c r="M65" t="s">
+        <v>25</v>
+      </c>
+      <c r="N65" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>303</v>
+      </c>
+      <c r="B66" t="s">
+        <v>304</v>
+      </c>
+      <c r="C66" t="s">
+        <v>305</v>
+      </c>
+      <c r="D66" t="s">
+        <v>306</v>
+      </c>
+      <c r="E66" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" t="s">
+        <v>32</v>
+      </c>
+      <c r="H66" t="s">
+        <v>307</v>
+      </c>
+      <c r="I66" t="s">
+        <v>22</v>
+      </c>
+      <c r="J66" t="s">
+        <v>33</v>
+      </c>
+      <c r="K66" t="s">
+        <v>34</v>
+      </c>
+      <c r="L66" t="s">
+        <v>35</v>
+      </c>
+      <c r="M66" t="s">
+        <v>36</v>
+      </c>
+      <c r="N66" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>308</v>
+      </c>
+      <c r="B67" t="s">
+        <v>309</v>
+      </c>
+      <c r="C67" t="s">
+        <v>310</v>
+      </c>
+      <c r="D67" t="s">
+        <v>311</v>
+      </c>
+      <c r="E67" t="s">
+        <v>46</v>
+      </c>
+      <c r="F67" t="s">
+        <v>51</v>
+      </c>
+      <c r="G67" t="s">
+        <v>32</v>
+      </c>
+      <c r="H67" t="s">
+        <v>312</v>
+      </c>
+      <c r="I67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J67" t="s">
+        <v>33</v>
+      </c>
+      <c r="K67" t="s">
+        <v>34</v>
+      </c>
+      <c r="L67" t="s">
+        <v>35</v>
+      </c>
+      <c r="M67" t="s">
+        <v>36</v>
+      </c>
+      <c r="N67" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>313</v>
+      </c>
+      <c r="B68" t="s">
+        <v>314</v>
+      </c>
+      <c r="C68" t="s">
+        <v>315</v>
+      </c>
+      <c r="D68" t="s">
+        <v>316</v>
+      </c>
+      <c r="E68" t="s">
+        <v>46</v>
+      </c>
+      <c r="F68" t="s">
+        <v>51</v>
+      </c>
+      <c r="G68" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68" t="s">
+        <v>278</v>
+      </c>
+      <c r="I68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J68" t="s">
+        <v>33</v>
+      </c>
+      <c r="K68" t="s">
+        <v>34</v>
+      </c>
+      <c r="L68" t="s">
+        <v>35</v>
+      </c>
+      <c r="M68" t="s">
+        <v>36</v>
+      </c>
+      <c r="N68" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>317</v>
+      </c>
+      <c r="B69" t="s">
+        <v>318</v>
+      </c>
+      <c r="C69" t="s">
+        <v>319</v>
+      </c>
+      <c r="D69" t="s">
+        <v>320</v>
+      </c>
+      <c r="E69" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" t="s">
+        <v>32</v>
+      </c>
+      <c r="H69" t="s">
+        <v>221</v>
+      </c>
+      <c r="I69" t="s">
+        <v>22</v>
+      </c>
+      <c r="J69" t="s">
+        <v>33</v>
+      </c>
+      <c r="K69" t="s">
+        <v>34</v>
+      </c>
+      <c r="L69" t="s">
+        <v>35</v>
+      </c>
+      <c r="M69" t="s">
+        <v>36</v>
+      </c>
+      <c r="N69" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>321</v>
+      </c>
+      <c r="B70" t="s">
+        <v>322</v>
+      </c>
+      <c r="C70" t="s">
+        <v>323</v>
+      </c>
+      <c r="D70" t="s">
+        <v>324</v>
+      </c>
+      <c r="E70" t="s">
+        <v>46</v>
+      </c>
+      <c r="F70" t="s">
+        <v>19</v>
+      </c>
+      <c r="G70" t="s">
+        <v>32</v>
+      </c>
+      <c r="H70" t="s">
+        <v>325</v>
+      </c>
+      <c r="I70" t="s">
+        <v>22</v>
+      </c>
+      <c r="J70" t="s">
+        <v>33</v>
+      </c>
+      <c r="K70" t="s">
+        <v>34</v>
+      </c>
+      <c r="L70" t="s">
+        <v>35</v>
+      </c>
+      <c r="M70" t="s">
+        <v>36</v>
+      </c>
+      <c r="N70" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>326</v>
+      </c>
+      <c r="B71" t="s">
+        <v>327</v>
+      </c>
+      <c r="C71" t="s">
+        <v>328</v>
+      </c>
+      <c r="D71" t="s">
+        <v>329</v>
+      </c>
+      <c r="E71" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" t="s">
+        <v>41</v>
+      </c>
+      <c r="G71" t="s">
+        <v>32</v>
+      </c>
+      <c r="H71" t="s">
+        <v>312</v>
+      </c>
+      <c r="I71" t="s">
+        <v>22</v>
+      </c>
+      <c r="J71" t="s">
+        <v>33</v>
+      </c>
+      <c r="K71" t="s">
+        <v>34</v>
+      </c>
+      <c r="L71" t="s">
+        <v>35</v>
+      </c>
+      <c r="M71" t="s">
+        <v>36</v>
+      </c>
+      <c r="N71" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>330</v>
+      </c>
+      <c r="B72" t="s">
+        <v>331</v>
+      </c>
+      <c r="C72" t="s">
+        <v>332</v>
+      </c>
+      <c r="D72" t="s">
+        <v>333</v>
+      </c>
+      <c r="E72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F72" t="s">
+        <v>19</v>
+      </c>
+      <c r="G72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" t="s">
+        <v>312</v>
+      </c>
+      <c r="I72" t="s">
+        <v>22</v>
+      </c>
+      <c r="J72" t="s">
+        <v>23</v>
+      </c>
+      <c r="K72" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" t="s">
+        <v>25</v>
+      </c>
+      <c r="M72" t="s">
+        <v>25</v>
+      </c>
+      <c r="N72" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>334</v>
+      </c>
+      <c r="B73" t="s">
+        <v>335</v>
+      </c>
+      <c r="C73" t="s">
+        <v>336</v>
+      </c>
+      <c r="D73" t="s">
+        <v>337</v>
+      </c>
+      <c r="E73" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" t="s">
+        <v>51</v>
+      </c>
+      <c r="G73" t="s">
+        <v>32</v>
+      </c>
+      <c r="H73" t="s">
+        <v>260</v>
+      </c>
+      <c r="I73" t="s">
+        <v>22</v>
+      </c>
+      <c r="J73" t="s">
+        <v>33</v>
+      </c>
+      <c r="K73" t="s">
+        <v>34</v>
+      </c>
+      <c r="L73" t="s">
+        <v>35</v>
+      </c>
+      <c r="M73" t="s">
+        <v>36</v>
+      </c>
+      <c r="N73" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>338</v>
+      </c>
+      <c r="B74" t="s">
+        <v>339</v>
+      </c>
+      <c r="C74" t="s">
+        <v>66</v>
+      </c>
+      <c r="D74" t="s">
+        <v>340</v>
+      </c>
+      <c r="E74" t="s">
+        <v>31</v>
+      </c>
+      <c r="F74" t="s">
+        <v>41</v>
+      </c>
+      <c r="G74" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" t="s">
+        <v>341</v>
+      </c>
+      <c r="I74" t="s">
+        <v>22</v>
+      </c>
+      <c r="J74" t="s">
+        <v>33</v>
+      </c>
+      <c r="K74" t="s">
+        <v>34</v>
+      </c>
+      <c r="L74" t="s">
+        <v>35</v>
+      </c>
+      <c r="M74" t="s">
+        <v>36</v>
+      </c>
+      <c r="N74" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>342</v>
+      </c>
+      <c r="B75" t="s">
+        <v>343</v>
+      </c>
+      <c r="C75" t="s">
+        <v>344</v>
+      </c>
+      <c r="D75" t="s">
+        <v>345</v>
+      </c>
+      <c r="E75" t="s">
+        <v>18</v>
+      </c>
+      <c r="F75" t="s">
+        <v>41</v>
+      </c>
+      <c r="G75" t="s">
+        <v>32</v>
+      </c>
+      <c r="H75" t="s">
+        <v>346</v>
+      </c>
+      <c r="I75" t="s">
+        <v>22</v>
+      </c>
+      <c r="J75" t="s">
+        <v>33</v>
+      </c>
+      <c r="K75" t="s">
+        <v>34</v>
+      </c>
+      <c r="L75" t="s">
+        <v>35</v>
+      </c>
+      <c r="M75" t="s">
+        <v>36</v>
+      </c>
+      <c r="N75" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>347</v>
+      </c>
+      <c r="B76" t="s">
+        <v>348</v>
+      </c>
+      <c r="C76" t="s">
+        <v>349</v>
+      </c>
+      <c r="D76" t="s">
+        <v>350</v>
+      </c>
+      <c r="E76" t="s">
+        <v>46</v>
+      </c>
+      <c r="F76" t="s">
+        <v>51</v>
+      </c>
+      <c r="G76" t="s">
+        <v>32</v>
+      </c>
+      <c r="H76" t="s">
+        <v>278</v>
+      </c>
+      <c r="I76" t="s">
+        <v>22</v>
+      </c>
+      <c r="J76" t="s">
+        <v>33</v>
+      </c>
+      <c r="K76" t="s">
+        <v>34</v>
+      </c>
+      <c r="L76" t="s">
+        <v>35</v>
+      </c>
+      <c r="M76" t="s">
+        <v>36</v>
+      </c>
+      <c r="N76" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>351</v>
+      </c>
+      <c r="B77" t="s">
+        <v>352</v>
+      </c>
+      <c r="C77" t="s">
+        <v>353</v>
+      </c>
+      <c r="D77" t="s">
+        <v>354</v>
+      </c>
+      <c r="E77" t="s">
+        <v>31</v>
+      </c>
+      <c r="F77" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77" t="s">
+        <v>355</v>
+      </c>
+      <c r="I77" t="s">
+        <v>22</v>
+      </c>
+      <c r="J77" t="s">
+        <v>33</v>
+      </c>
+      <c r="K77" t="s">
+        <v>34</v>
+      </c>
+      <c r="L77" t="s">
+        <v>35</v>
+      </c>
+      <c r="M77" t="s">
+        <v>36</v>
+      </c>
+      <c r="N77" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>356</v>
+      </c>
+      <c r="B78" t="s">
+        <v>357</v>
+      </c>
+      <c r="C78" t="s">
+        <v>125</v>
+      </c>
+      <c r="D78" t="s">
+        <v>358</v>
+      </c>
+      <c r="E78" t="s">
+        <v>46</v>
+      </c>
+      <c r="F78" t="s">
+        <v>41</v>
+      </c>
+      <c r="G78" t="s">
+        <v>32</v>
+      </c>
+      <c r="H78" t="s">
+        <v>265</v>
+      </c>
+      <c r="I78" t="s">
+        <v>22</v>
+      </c>
+      <c r="J78" t="s">
+        <v>33</v>
+      </c>
+      <c r="K78" t="s">
+        <v>34</v>
+      </c>
+      <c r="L78" t="s">
+        <v>35</v>
+      </c>
+      <c r="M78" t="s">
+        <v>36</v>
+      </c>
+      <c r="N78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>359</v>
+      </c>
+      <c r="B79" t="s">
+        <v>360</v>
+      </c>
+      <c r="C79" t="s">
+        <v>29</v>
+      </c>
+      <c r="D79" t="s">
+        <v>361</v>
+      </c>
+      <c r="E79" t="s">
+        <v>31</v>
+      </c>
+      <c r="F79" t="s">
+        <v>51</v>
+      </c>
+      <c r="G79" t="s">
+        <v>63</v>
+      </c>
+      <c r="H79" t="s">
+        <v>231</v>
+      </c>
+      <c r="I79" t="s">
+        <v>22</v>
+      </c>
+      <c r="J79" t="s">
+        <v>33</v>
+      </c>
+      <c r="K79" t="s">
+        <v>24</v>
+      </c>
+      <c r="L79" t="s">
+        <v>25</v>
+      </c>
+      <c r="M79" t="s">
+        <v>25</v>
+      </c>
+      <c r="N79" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>362</v>
+      </c>
+      <c r="B80" t="s">
+        <v>363</v>
+      </c>
+      <c r="C80" t="s">
+        <v>364</v>
+      </c>
+      <c r="D80" t="s">
+        <v>365</v>
+      </c>
+      <c r="E80" t="s">
+        <v>46</v>
+      </c>
+      <c r="F80" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" t="s">
+        <v>32</v>
+      </c>
+      <c r="H80" t="s">
+        <v>325</v>
+      </c>
+      <c r="I80" t="s">
+        <v>22</v>
+      </c>
+      <c r="J80" t="s">
+        <v>33</v>
+      </c>
+      <c r="K80" t="s">
+        <v>34</v>
+      </c>
+      <c r="L80" t="s">
+        <v>35</v>
+      </c>
+      <c r="M80" t="s">
+        <v>36</v>
+      </c>
+      <c r="N80" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>366</v>
+      </c>
+      <c r="B81" t="s">
+        <v>367</v>
+      </c>
+      <c r="C81" t="s">
+        <v>368</v>
+      </c>
+      <c r="D81" t="s">
+        <v>369</v>
+      </c>
+      <c r="E81" t="s">
+        <v>31</v>
+      </c>
+      <c r="F81" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" t="s">
+        <v>32</v>
+      </c>
+      <c r="H81" t="s">
+        <v>346</v>
+      </c>
+      <c r="I81" t="s">
+        <v>22</v>
+      </c>
+      <c r="J81" t="s">
+        <v>33</v>
+      </c>
+      <c r="K81" t="s">
+        <v>34</v>
+      </c>
+      <c r="L81" t="s">
+        <v>35</v>
+      </c>
+      <c r="M81" t="s">
+        <v>36</v>
+      </c>
+      <c r="N81" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>370</v>
+      </c>
+      <c r="B82" t="s">
+        <v>371</v>
+      </c>
+      <c r="C82" t="s">
+        <v>372</v>
+      </c>
+      <c r="D82" t="s">
+        <v>373</v>
+      </c>
+      <c r="E82" t="s">
+        <v>46</v>
+      </c>
+      <c r="F82" t="s">
+        <v>51</v>
+      </c>
+      <c r="G82" t="s">
+        <v>32</v>
+      </c>
+      <c r="H82" t="s">
+        <v>374</v>
+      </c>
+      <c r="I82" t="s">
+        <v>375</v>
+      </c>
+      <c r="J82" t="s">
+        <v>376</v>
+      </c>
+      <c r="K82" t="s">
+        <v>377</v>
+      </c>
+      <c r="L82" t="s">
+        <v>35</v>
+      </c>
+      <c r="M82" t="s">
+        <v>25</v>
+      </c>
+      <c r="N82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>378</v>
+      </c>
+      <c r="B83" t="s">
+        <v>379</v>
+      </c>
+      <c r="C83" t="s">
+        <v>380</v>
+      </c>
+      <c r="D83" t="s">
+        <v>381</v>
+      </c>
+      <c r="E83" t="s">
+        <v>31</v>
+      </c>
+      <c r="F83" t="s">
+        <v>51</v>
+      </c>
+      <c r="G83" t="s">
+        <v>32</v>
+      </c>
+      <c r="H83" t="s">
+        <v>374</v>
+      </c>
+      <c r="I83" t="s">
+        <v>375</v>
+      </c>
+      <c r="J83" t="s">
+        <v>382</v>
+      </c>
+      <c r="K83" t="s">
+        <v>383</v>
+      </c>
+      <c r="L83" t="s">
+        <v>384</v>
+      </c>
+      <c r="M83" t="s">
+        <v>385</v>
+      </c>
+      <c r="N83" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>386</v>
+      </c>
+      <c r="B84" t="s">
+        <v>387</v>
+      </c>
+      <c r="C84" t="s">
+        <v>388</v>
+      </c>
+      <c r="D84" t="s">
+        <v>389</v>
+      </c>
+      <c r="E84" t="s">
+        <v>18</v>
+      </c>
+      <c r="F84" t="s">
+        <v>51</v>
+      </c>
+      <c r="G84" t="s">
+        <v>32</v>
+      </c>
+      <c r="H84" t="s">
+        <v>374</v>
+      </c>
+      <c r="I84" t="s">
+        <v>375</v>
+      </c>
+      <c r="J84" t="s">
+        <v>390</v>
+      </c>
+      <c r="K84" t="s">
+        <v>391</v>
+      </c>
+      <c r="L84" t="s">
+        <v>25</v>
+      </c>
+      <c r="M84" t="s">
+        <v>25</v>
+      </c>
+      <c r="N84" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
